--- a/metadata/Plate5/SRKW_Diet_Plate5_MetaData.xlsx
+++ b/metadata/Plate5/SRKW_Diet_Plate5_MetaData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lfallon/Library/Application Support/Box/Box Edit/Documents/2185572405481/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D37667-AD52-244F-8552-D2CF91E538CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A7E22D-EC55-5040-8786-AE00D7BFD703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6200" yWindow="680" windowWidth="20580" windowHeight="22820" xr2:uid="{518B7A33-C5FE-E642-B8D5-47A99A98280E}"/>
+    <workbookView xWindow="26860" yWindow="600" windowWidth="18720" windowHeight="22820" xr2:uid="{518B7A33-C5FE-E642-B8D5-47A99A98280E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="122">
   <si>
     <t>Sample_name</t>
   </si>
@@ -399,13 +399,16 @@
   </si>
   <si>
     <t>Feb</t>
+  </si>
+  <si>
+    <t>L108</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -425,6 +428,18 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow (Body)"/>
     </font>
   </fonts>
   <fills count="2">
@@ -448,14 +463,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -964,6 +981,9 @@
       <c r="B9" t="s">
         <v>37</v>
       </c>
+      <c r="C9" s="3" t="s">
+        <v>121</v>
+      </c>
       <c r="D9">
         <v>2013</v>
       </c>
@@ -1241,6 +1261,9 @@
       <c r="B23" t="s">
         <v>51</v>
       </c>
+      <c r="C23" s="4" t="s">
+        <v>108</v>
+      </c>
       <c r="D23">
         <v>2014</v>
       </c>
@@ -1394,6 +1417,9 @@
       </c>
       <c r="B31" t="s">
         <v>59</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="D31">
         <v>2016</v>
